--- a/data/trans_orig/IP11C$ingresado-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP11C$ingresado-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -944,112 +944,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>10678</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>2703</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5540</t>
+          <t>13396</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>17550</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>67,16%</t>
         </is>
       </c>
     </row>
@@ -1057,112 +1057,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7948</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>6198</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2143</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4994</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>16,18%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>37,71%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5449</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2720</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8398</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>41,14%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>20,54%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>63,42%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13396</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17589</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>36,98%</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1410,102 +1410,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>10596</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>12501</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>13617</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2849</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>16728</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>80,63%</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1523,102 +1523,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10596</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12499</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>13617</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16620</t>
+          <t>8960</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>43,19%</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -1856,112 +1856,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>12662</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -1969,112 +1969,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4584</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>42,64%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>10,87%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>72,4%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4257</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>15,78%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>47,86%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>3632</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1650</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>5630</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>57,36%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>26,05%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>88,92%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>6277</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>8171</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>70,56%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>41,72%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>91,87%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>12628</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>48,99%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -2312,112 +2312,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>16871</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -2425,112 +2425,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>793</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>14112</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10440</t>
+          <t>575</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16855</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11613</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15907</t>
+          <t>16421</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -2768,112 +2768,112 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>21408</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>25613</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>29626</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>24536</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>34588</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>77</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>51034</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11547</t>
+          <t>43669</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>57426</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>70,18%</t>
         </is>
       </c>
     </row>
@@ -2881,112 +2881,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>21408</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16940</t>
+          <t>5782</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26030</t>
+          <t>14713</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>29626</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24310</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34737</t>
+          <t>12342</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>51034</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43009</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>57257</t>
+          <t>23448</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>813</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -3456,112 +3456,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3608</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>18910</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>74,32%</t>
         </is>
       </c>
     </row>
@@ -3569,112 +3569,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11953</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>37,22%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4462</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>606</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>810</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>7284</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -3912,112 +3912,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>11306</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11286</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>12261</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>15439</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11119</t>
+          <t>23568</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>18324</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>28204</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>68,91%</t>
         </is>
       </c>
     </row>
@@ -4025,112 +4025,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11306</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15265</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15637</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>23568</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18297</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28335</t>
+          <t>15696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -4368,112 +4368,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6190</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>11631</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>9880</t>
+          <t>11734</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>15878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>59,6%</t>
         </is>
       </c>
     </row>
@@ -4481,112 +4481,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12006</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>11734</t>
+          <t>9880</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7860</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>52,36%</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -4824,112 +4824,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11158</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>12607</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>15774</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>12986</t>
+          <t>17192</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>12542</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17884</t>
+          <t>21879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -4937,112 +4937,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7599</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16237</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>17192</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21788</t>
+          <t>18026</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>56,19%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14751</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>12435</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>16233</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -5280,112 +5280,112 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>25402</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15090</t>
+          <t>19123</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26797</t>
+          <t>31080</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18558</t>
+          <t>41772</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>34859</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25075</t>
+          <t>48560</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>96</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>39538</t>
+          <t>67174</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31581</t>
+          <t>58216</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48464</t>
+          <t>76037</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>60,79%</t>
         </is>
       </c>
     </row>
@@ -5393,112 +5393,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>25402</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20223</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31799</t>
+          <t>27624</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>41772</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34579</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48331</t>
+          <t>24956</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>58</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>67174</t>
+          <t>39538</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>57634</t>
+          <t>31462</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>76231</t>
+          <t>48005</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -5968,112 +5968,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>12873</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>15347</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>90,41%</t>
         </is>
       </c>
     </row>
@@ -6081,112 +6081,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>817</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9129</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>817</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15373</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -6424,17 +6424,17 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -6464,72 +6464,72 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>19396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -6537,17 +6537,17 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -6577,72 +6577,72 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10427</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>17449</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14094</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -6880,112 +6880,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>11893</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -6993,112 +6993,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>634</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>10610</t>
+          <t>634</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11884</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7278,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -7336,17 +7336,17 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -7376,72 +7376,72 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>12628</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -7449,17 +7449,17 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>738</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -7489,72 +7489,72 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10400</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13256</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>48,71%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>475</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7742</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>741</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>980</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -7792,112 +7792,112 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>20890</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17133</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>30392</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>25204</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>34525</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>76</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>51282</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>45339</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11910</t>
+          <t>56135</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -7905,112 +7905,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>20890</t>
+          <t>738</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17772</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22752</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>30392</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25073</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34505</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>51282</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>45684</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>56366</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>51,64%</t>
         </is>
       </c>
     </row>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>45,12%</t>
         </is>
       </c>
     </row>
@@ -8480,112 +8480,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>886</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2369</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -8593,112 +8593,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>652</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>652</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>47,54%</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>52,87%</t>
         </is>
       </c>
     </row>
@@ -8936,112 +8936,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -9049,112 +9049,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>877</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>877</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9809</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>36,7%</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>38,34%</t>
         </is>
       </c>
     </row>
@@ -9392,112 +9392,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>90,36%</t>
         </is>
       </c>
     </row>
@@ -9505,112 +9505,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>762</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>761</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -9848,17 +9848,17 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -9888,72 +9888,72 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -9961,17 +9961,17 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10001,72 +10001,72 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>709</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>709</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6083</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>398</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -10304,112 +10304,112 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>19726</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15164</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>22468</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>31444</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>35896</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -10417,112 +10417,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11718</t>
+          <t>2291</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>709</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25883</t>
+          <t>829</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>35922</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
